--- a/data/final/series/comexstat_comex_importacoes_cif_usd.xlsx
+++ b/data/final/series/comexstat_comex_importacoes_cif_usd.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B81"/>
+  <dimension ref="A1:B82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1013,7 +1013,7 @@
         <v>46053</v>
       </c>
       <c r="B74" t="n">
-        <v>21798118603</v>
+        <v>21770708569</v>
       </c>
     </row>
     <row r="75">
@@ -1021,7 +1021,7 @@
         <v>46081</v>
       </c>
       <c r="B75" t="n">
-        <v>23125218423</v>
+        <v>23127724322</v>
       </c>
     </row>
     <row r="76">
@@ -1029,7 +1029,7 @@
         <v>46112</v>
       </c>
       <c r="B76" t="n">
-        <v>26435269841</v>
+        <v>26435490226</v>
       </c>
     </row>
     <row r="77">
@@ -1037,7 +1037,7 @@
         <v>46142</v>
       </c>
       <c r="B77" t="n">
-        <v>24767217155</v>
+        <v>24770827669</v>
       </c>
     </row>
     <row r="78">
@@ -1045,7 +1045,7 @@
         <v>46173</v>
       </c>
       <c r="B78" t="n">
-        <v>25371585804</v>
+        <v>25373660998</v>
       </c>
     </row>
     <row r="79">
@@ -1053,7 +1053,7 @@
         <v>46203</v>
       </c>
       <c r="B79" t="n">
-        <v>27840717215</v>
+        <v>27842007017</v>
       </c>
     </row>
     <row r="80">
@@ -1061,7 +1061,7 @@
         <v>46234</v>
       </c>
       <c r="B80" t="n">
-        <v>28655667843</v>
+        <v>28656745438</v>
       </c>
     </row>
     <row r="81">
@@ -1069,7 +1069,15 @@
         <v>46265</v>
       </c>
       <c r="B81" t="n">
-        <v>27331288667</v>
+        <v>27389709115</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B82" t="n">
+        <v>28316206132</v>
       </c>
     </row>
   </sheetData>
